--- a/mlb_weather_professional_2026_07_11.xlsx
+++ b/mlb_weather_professional_2026_07_11.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2132" uniqueCount="450">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2132" uniqueCount="451">
   <si>
     <t>Date</t>
   </si>
@@ -734,67 +734,64 @@
     <t>Dodger Stadium</t>
   </si>
   <si>
-    <t>🔥 Excellent</t>
+    <t>🟢 Good</t>
   </si>
   <si>
     <t>🟢 Very Good</t>
   </si>
   <si>
+    <t>🔴 Poor</t>
+  </si>
+  <si>
     <t>🟨 Neutral</t>
   </si>
   <si>
-    <t>🚀 Elite</t>
-  </si>
-  <si>
-    <t>🟢 Good</t>
-  </si>
-  <si>
-    <t>adjusted carry 80.4; +17 ft carry; +7.3% HR env.; high delay risk 74</t>
-  </si>
-  <si>
-    <t>adjusted carry 89.2; +22 ft carry; +9.4% HR env.; elevated delay risk 50</t>
-  </si>
-  <si>
-    <t>adjusted carry 76.9; +15 ft carry; +6.5% HR env.; high delay risk 74</t>
-  </si>
-  <si>
-    <t>adjusted carry 81.1; +17 ft carry; +7.5% HR env.; high delay risk 70</t>
-  </si>
-  <si>
-    <t>adjusted carry 59.4; +5 ft carry; +2.3% HR env.; high delay risk 74</t>
-  </si>
-  <si>
-    <t>adjusted carry 85.3; +19 ft carry; +8.5% HR env.; high delay risk 62</t>
-  </si>
-  <si>
-    <t>adjusted carry 81.6; +17 ft carry; +7.6% HR env.; high delay risk 61</t>
-  </si>
-  <si>
-    <t>adjusted carry 87.5; +21 ft carry; +9.0% HR env.; high delay risk 68</t>
-  </si>
-  <si>
-    <t>adjusted carry 88.1; +21 ft carry; +9.1% HR env.; high delay risk 70</t>
-  </si>
-  <si>
-    <t>adjusted carry 81.7; +17 ft carry; +7.6% HR env.; elevated delay risk 51</t>
-  </si>
-  <si>
-    <t>adjusted carry 77.5; +15 ft carry; +6.6% HR env.; high delay risk 82</t>
-  </si>
-  <si>
-    <t>adjusted carry 94.7; +25 ft carry; +10.7% HR env.; elevated delay risk 42</t>
-  </si>
-  <si>
-    <t>adjusted carry 77.0; +15 ft carry; +6.5% HR env.; high delay risk 87</t>
-  </si>
-  <si>
-    <t>adjusted carry 78.0; +15 ft carry; +6.7% HR env.; high delay risk 84</t>
-  </si>
-  <si>
-    <t>adjusted carry 68.2; +10 ft carry; +4.4% HR env.; high delay risk 78</t>
-  </si>
-  <si>
-    <t>adjusted carry 79.7; +16 ft carry; +7.1% HR env.; elevated delay risk 59</t>
+    <t>🟧 Below Average</t>
+  </si>
+  <si>
+    <t>adjusted carry 61.1; +6 ft carry; +2.7% HR env.</t>
+  </si>
+  <si>
+    <t>adjusted carry 79.1; +16 ft carry; +7.0% HR env.</t>
+  </si>
+  <si>
+    <t>adjusted carry 31.5; -10 ft carry; -4.4% HR env.</t>
+  </si>
+  <si>
+    <t>adjusted carry 60.4; +6 ft carry; +2.5% HR env.</t>
+  </si>
+  <si>
+    <t>adjusted carry 56.3; +3 ft carry; +1.5% HR env.</t>
+  </si>
+  <si>
+    <t>adjusted carry 55.0; +3 ft carry; +1.2% HR env.; elevated delay risk 40</t>
+  </si>
+  <si>
+    <t>adjusted carry 54.9; +3 ft carry; +1.2% HR env.</t>
+  </si>
+  <si>
+    <t>adjusted carry 54.4; +2 ft carry; +1.1% HR env.; roof-controlled environment</t>
+  </si>
+  <si>
+    <t>adjusted carry 54.5; +2 ft carry; +1.1% HR env.; roof-controlled environment</t>
+  </si>
+  <si>
+    <t>adjusted carry 41.8; -5 ft carry; -2.0% HR env.</t>
+  </si>
+  <si>
+    <t>adjusted carry 46.2; -2 ft carry; -0.9% HR env.; elevated delay risk 45</t>
+  </si>
+  <si>
+    <t>adjusted carry 54.9; +3 ft carry; +1.2% HR env.; roof-controlled environment</t>
+  </si>
+  <si>
+    <t>adjusted carry 57.2; +4 ft carry; +1.7% HR env.</t>
+  </si>
+  <si>
+    <t>adjusted carry 47.2; -2 ft carry; -0.7% HR env.; elevated delay risk 51</t>
+  </si>
+  <si>
+    <t>adjusted carry 70.3; +11 ft carry; +4.9% HR env.</t>
   </si>
   <si>
     <t>88th</t>
@@ -854,49 +851,52 @@
     <t>C</t>
   </si>
   <si>
-    <t>2026-07-11 01:54:30 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-11 01:54:31 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-11 01:54:32 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-11 01:54:33 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-11 01:54:34 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-11 01:54:35 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-11 01:54:36 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-11 01:54:37 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-11 01:54:38 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-11 01:54:39 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-11 01:54:40 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-11 01:54:41 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-11 01:54:42 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-11 01:54:43 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-11 01:54:44 PM PDT</t>
+    <t>2026-07-11 01:56:29 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-11 01:56:30 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-11 01:56:31 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-11 01:56:32 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-11 01:56:33 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-11 01:56:34 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-11 01:56:35 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-11 01:56:37 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-11 01:56:38 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-11 01:56:39 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-11 01:56:40 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-11 01:56:42 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-11 01:56:43 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-11 01:56:44 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-11 01:56:45 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-11 01:56:47 PM PDT</t>
   </si>
   <si>
     <t>MODERATE</t>
@@ -974,55 +974,58 @@
     <t>Code 30</t>
   </si>
   <si>
-    <t>2026-07-11 20:54:30 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-11 20:54:31 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-11 20:54:32 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-11 20:54:33 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-11 20:54:34 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-11 20:54:35 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-11 20:54:36 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-11 20:54:37 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-11 20:54:38 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-11 20:54:39 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-11 20:54:40 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-11 20:54:41 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-11 20:54:42 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-11 20:54:43 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-11 20:54:44 UTC</t>
+    <t>2026-07-11 20:56:29 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-11 20:56:30 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-11 20:56:31 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-11 20:56:32 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-11 20:56:33 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-11 20:56:34 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-11 20:56:35 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-11 20:56:37 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-11 20:56:38 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-11 20:56:39 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-11 20:56:40 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-11 20:56:42 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-11 20:56:43 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-11 20:56:44 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-11 20:56:45 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-11 20:56:47 UTC</t>
   </si>
   <si>
     <t>2026-07-11T18:21:38+00:00</t>
   </si>
   <si>
-    <t>2026-07-11T20:44:22+00:00</t>
+    <t>2026-07-11T19:06:40+00:00</t>
   </si>
   <si>
     <t>2026-07-11T20:51:19+00:00</t>
@@ -1064,34 +1067,34 @@
     <t>N</t>
   </si>
   <si>
+    <t>S</t>
+  </si>
+  <si>
+    <t>NNE</t>
+  </si>
+  <si>
+    <t>WSW</t>
+  </si>
+  <si>
+    <t>NW</t>
+  </si>
+  <si>
+    <t>E</t>
+  </si>
+  <si>
+    <t>SW</t>
+  </si>
+  <si>
+    <t>ENE</t>
+  </si>
+  <si>
+    <t>NE</t>
+  </si>
+  <si>
+    <t>W</t>
+  </si>
+  <si>
     <t>SSW</t>
-  </si>
-  <si>
-    <t>NNE</t>
-  </si>
-  <si>
-    <t>WSW</t>
-  </si>
-  <si>
-    <t>NW</t>
-  </si>
-  <si>
-    <t>E</t>
-  </si>
-  <si>
-    <t>SW</t>
-  </si>
-  <si>
-    <t>ENE</t>
-  </si>
-  <si>
-    <t>NE</t>
-  </si>
-  <si>
-    <t>S</t>
-  </si>
-  <si>
-    <t>W</t>
   </si>
   <si>
     <t>WNW</t>
@@ -1837,7 +1840,7 @@
     <col min="6" max="6" width="19.7109375" customWidth="1"/>
     <col min="7" max="7" width="29.7109375" customWidth="1"/>
     <col min="8" max="8" width="19.7109375" customWidth="1"/>
-    <col min="9" max="9" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="17.7109375" customWidth="1"/>
     <col min="10" max="10" width="34.7109375" customWidth="1"/>
     <col min="11" max="11" width="17.7109375" customWidth="1"/>
     <col min="12" max="12" width="27.7109375" customWidth="1"/>
@@ -2462,10 +2465,10 @@
         <v>61.1</v>
       </c>
       <c r="M2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="N2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="O2">
         <v>6</v>
@@ -2489,10 +2492,10 @@
         <v>1.029</v>
       </c>
       <c r="V2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="W2">
-        <v>152.9</v>
+        <v>154.9</v>
       </c>
       <c r="X2">
         <v>5</v>
@@ -2555,7 +2558,7 @@
         <v>317</v>
       </c>
       <c r="AR2" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AS2">
         <v>0.92</v>
@@ -2633,7 +2636,7 @@
         <v>5</v>
       </c>
       <c r="BR2" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="BS2">
         <v>-1.5</v>
@@ -2702,7 +2705,7 @@
         <v>5.2</v>
       </c>
       <c r="CO2" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="CP2">
         <v>-1.2</v>
@@ -2771,7 +2774,7 @@
         <v>5.1</v>
       </c>
       <c r="DL2" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="DM2">
         <v>-1.3</v>
@@ -2840,7 +2843,7 @@
         <v>5.7</v>
       </c>
       <c r="EI2" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="EJ2">
         <v>-1.4</v>
@@ -2911,25 +2914,25 @@
         <v>223</v>
       </c>
       <c r="H3" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="I3" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="J3" t="s">
         <v>243</v>
       </c>
       <c r="K3">
-        <v>81.3</v>
+        <v>82.3</v>
       </c>
       <c r="L3">
-        <v>79.3</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="M3" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="N3" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="O3">
         <v>16</v>
@@ -2938,52 +2941,52 @@
         <v>7</v>
       </c>
       <c r="Q3" s="1">
-        <v>81.3</v>
+        <v>82.3</v>
       </c>
       <c r="R3">
-        <v>79.3</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="S3">
-        <v>93.7</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="T3">
         <v>10.2</v>
       </c>
       <c r="U3" s="2">
-        <v>1.075</v>
+        <v>1.077</v>
       </c>
       <c r="V3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="W3">
-        <v>10.2</v>
+        <v>109.8</v>
       </c>
       <c r="X3">
         <v>5</v>
       </c>
       <c r="Y3" s="1">
-        <v>78.90000000000001</v>
+        <v>78.8</v>
       </c>
       <c r="Z3" s="1">
-        <v>82.2</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="AA3">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="AB3">
-        <v>2853</v>
+        <v>2829</v>
       </c>
       <c r="AC3" t="s">
         <v>293</v>
       </c>
       <c r="AD3">
-        <v>14.3</v>
+        <v>15.8</v>
       </c>
       <c r="AE3" t="s">
         <v>293</v>
       </c>
       <c r="AF3">
-        <v>5.6</v>
+        <v>11.1</v>
       </c>
       <c r="AG3" t="s">
         <v>297</v>
@@ -3019,7 +3022,7 @@
         <v>318</v>
       </c>
       <c r="AR3" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AS3">
         <v>0.92</v>
@@ -3031,55 +3034,55 @@
         <v>0</v>
       </c>
       <c r="AV3">
-        <v>89.2</v>
+        <v>88.8</v>
       </c>
       <c r="AW3">
-        <v>67.8</v>
+        <v>67.2</v>
       </c>
       <c r="AX3">
-        <v>50</v>
+        <v>49.1</v>
       </c>
       <c r="AY3">
         <v>988</v>
       </c>
       <c r="AZ3">
-        <v>5.6</v>
+        <v>7.3</v>
       </c>
       <c r="BA3">
         <v>10.8</v>
       </c>
       <c r="BB3">
-        <v>5.6</v>
+        <v>7.2</v>
       </c>
       <c r="BC3">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="BD3">
-        <v>1.1187</v>
+        <v>1.1197</v>
       </c>
       <c r="BE3">
-        <v>58.1</v>
+        <v>59.4</v>
       </c>
       <c r="BF3">
-        <v>57.6</v>
+        <v>57.7</v>
       </c>
       <c r="BG3">
-        <v>51.4</v>
+        <v>52.4</v>
       </c>
       <c r="BH3">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="BI3">
         <v>-0.8</v>
       </c>
       <c r="BJ3">
-        <v>88.40000000000001</v>
+        <v>88</v>
       </c>
       <c r="BK3">
-        <v>68.7</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="BL3">
-        <v>52.7</v>
+        <v>51.9</v>
       </c>
       <c r="BM3">
         <v>988.2</v>
@@ -3088,67 +3091,67 @@
         <v>35</v>
       </c>
       <c r="BO3">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BP3">
-        <v>5.7</v>
+        <v>7.3</v>
       </c>
       <c r="BQ3">
         <v>10.8</v>
       </c>
       <c r="BR3" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="BS3">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="BT3">
-        <v>5.7</v>
+        <v>7.2</v>
       </c>
       <c r="BU3">
-        <v>2.1</v>
+        <v>1.3</v>
       </c>
       <c r="BV3">
-        <v>1.1203</v>
+        <v>1.1214</v>
       </c>
       <c r="BW3">
-        <v>2792</v>
+        <v>2764</v>
       </c>
       <c r="BX3">
-        <v>81.2</v>
+        <v>81.8</v>
       </c>
       <c r="BY3">
-        <v>1.075</v>
+        <v>1.076</v>
       </c>
       <c r="BZ3">
-        <v>78.8</v>
+        <v>78.3</v>
       </c>
       <c r="CA3">
-        <v>82.09999999999999</v>
+        <v>83.7</v>
       </c>
       <c r="CB3">
-        <v>78.90000000000001</v>
+        <v>78.5</v>
       </c>
       <c r="CC3">
-        <v>92.7</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="CD3">
         <v>9.5</v>
       </c>
       <c r="CE3">
-        <v>12</v>
+        <v>14.6</v>
       </c>
       <c r="CF3" t="s">
         <v>293</v>
       </c>
       <c r="CG3">
-        <v>89.40000000000001</v>
+        <v>89</v>
       </c>
       <c r="CH3">
-        <v>67.2</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="CI3">
-        <v>48.6</v>
+        <v>47.8</v>
       </c>
       <c r="CJ3">
         <v>988.1</v>
@@ -3157,67 +3160,67 @@
         <v>28.8</v>
       </c>
       <c r="CL3">
-        <v>1.3</v>
+        <v>4.8</v>
       </c>
       <c r="CM3">
-        <v>5.8</v>
+        <v>7.3</v>
       </c>
       <c r="CN3">
         <v>10.7</v>
       </c>
       <c r="CO3" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="CP3">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="CQ3">
-        <v>5.8</v>
+        <v>7.2</v>
       </c>
       <c r="CR3">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="CS3">
-        <v>1.1186</v>
+        <v>1.1197</v>
       </c>
       <c r="CT3">
-        <v>2863</v>
+        <v>2836</v>
       </c>
       <c r="CU3">
-        <v>81.59999999999999</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="CV3">
-        <v>1.076</v>
+        <v>1.078</v>
       </c>
       <c r="CW3">
-        <v>79.09999999999999</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="CX3">
-        <v>82.59999999999999</v>
+        <v>84.3</v>
       </c>
       <c r="CY3">
-        <v>79.8</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="CZ3">
-        <v>94.09999999999999</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="DA3">
         <v>10.5</v>
       </c>
       <c r="DB3">
-        <v>13.1</v>
+        <v>15</v>
       </c>
       <c r="DC3" t="s">
         <v>293</v>
       </c>
       <c r="DD3">
-        <v>89.90000000000001</v>
+        <v>89.5</v>
       </c>
       <c r="DE3">
-        <v>67.09999999999999</v>
+        <v>66.5</v>
       </c>
       <c r="DF3">
-        <v>47.8</v>
+        <v>46.9</v>
       </c>
       <c r="DG3">
         <v>987.5</v>
@@ -3226,55 +3229,55 @@
         <v>20.6</v>
       </c>
       <c r="DI3">
-        <v>1.8</v>
+        <v>4.8</v>
       </c>
       <c r="DJ3">
-        <v>5.5</v>
+        <v>7.2</v>
       </c>
       <c r="DK3">
         <v>10.7</v>
       </c>
       <c r="DL3" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="DM3">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="DN3">
-        <v>5.5</v>
+        <v>7.1</v>
       </c>
       <c r="DO3">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="DP3">
-        <v>1.117</v>
+        <v>1.118</v>
       </c>
       <c r="DQ3">
-        <v>2918</v>
+        <v>2890</v>
       </c>
       <c r="DR3">
-        <v>81.8</v>
+        <v>82.7</v>
       </c>
       <c r="DS3">
-        <v>1.076</v>
+        <v>1.078</v>
       </c>
       <c r="DT3">
+        <v>79.2</v>
+      </c>
+      <c r="DU3">
+        <v>84.5</v>
+      </c>
+      <c r="DV3">
         <v>79.5</v>
       </c>
-      <c r="DU3">
-        <v>82.7</v>
-      </c>
-      <c r="DV3">
-        <v>80.40000000000001</v>
-      </c>
       <c r="DW3">
-        <v>95.40000000000001</v>
+        <v>90.2</v>
       </c>
       <c r="DX3">
         <v>9.9</v>
       </c>
       <c r="DY3">
-        <v>13.7</v>
+        <v>15.4</v>
       </c>
       <c r="DZ3" t="s">
         <v>293</v>
@@ -3283,10 +3286,10 @@
         <v>90.2</v>
       </c>
       <c r="EB3">
-        <v>67.09999999999999</v>
+        <v>66.5</v>
       </c>
       <c r="EC3">
-        <v>47.4</v>
+        <v>46.1</v>
       </c>
       <c r="ED3">
         <v>987.4</v>
@@ -3295,55 +3298,55 @@
         <v>30.7</v>
       </c>
       <c r="EF3">
-        <v>2.3</v>
+        <v>5</v>
       </c>
       <c r="EG3">
-        <v>4.9</v>
+        <v>7</v>
       </c>
       <c r="EH3">
         <v>10.5</v>
       </c>
       <c r="EI3" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="EJ3">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="EK3">
-        <v>4.9</v>
+        <v>6.9</v>
       </c>
       <c r="EL3">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="EM3">
-        <v>1.1162</v>
+        <v>1.1164</v>
       </c>
       <c r="EN3">
         <v>2941</v>
       </c>
       <c r="EO3">
+        <v>82.7</v>
+      </c>
+      <c r="EP3">
+        <v>1.079</v>
+      </c>
+      <c r="EQ3">
         <v>79.40000000000001</v>
       </c>
-      <c r="EP3">
-        <v>1.071</v>
-      </c>
-      <c r="EQ3">
-        <v>77</v>
-      </c>
       <c r="ER3">
-        <v>80.7</v>
+        <v>84.5</v>
       </c>
       <c r="ES3">
-        <v>77.40000000000001</v>
+        <v>79.2</v>
       </c>
       <c r="ET3">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="EU3">
         <v>13</v>
       </c>
       <c r="EV3">
-        <v>14.3</v>
+        <v>15.8</v>
       </c>
       <c r="EW3" t="s">
         <v>293</v>
@@ -3375,10 +3378,10 @@
         <v>224</v>
       </c>
       <c r="H4" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="I4" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="J4" t="s">
         <v>244</v>
@@ -3390,10 +3393,10 @@
         <v>31.5</v>
       </c>
       <c r="M4" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="N4" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="O4">
         <v>-10</v>
@@ -3417,10 +3420,10 @@
         <v>0.948</v>
       </c>
       <c r="V4" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="W4">
-        <v>3.2</v>
+        <v>5.2</v>
       </c>
       <c r="X4">
         <v>5</v>
@@ -3483,7 +3486,7 @@
         <v>319</v>
       </c>
       <c r="AR4" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AS4">
         <v>0.92</v>
@@ -3561,7 +3564,7 @@
         <v>17.2</v>
       </c>
       <c r="BR4" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="BS4">
         <v>-11.1</v>
@@ -3630,7 +3633,7 @@
         <v>17.7</v>
       </c>
       <c r="CO4" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="CP4">
         <v>-11.4</v>
@@ -3699,7 +3702,7 @@
         <v>18.9</v>
       </c>
       <c r="DL4" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="DM4">
         <v>-12.1</v>
@@ -3768,7 +3771,7 @@
         <v>17.9</v>
       </c>
       <c r="EI4" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="EJ4">
         <v>-11.6</v>
@@ -3854,10 +3857,10 @@
         <v>60.4</v>
       </c>
       <c r="M5" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="N5" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="O5">
         <v>6</v>
@@ -3881,10 +3884,10 @@
         <v>1.028</v>
       </c>
       <c r="V5" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="W5">
-        <v>152.9</v>
+        <v>154.9</v>
       </c>
       <c r="X5">
         <v>5</v>
@@ -3947,7 +3950,7 @@
         <v>320</v>
       </c>
       <c r="AR5" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AS5">
         <v>0.92</v>
@@ -4025,7 +4028,7 @@
         <v>5.9</v>
       </c>
       <c r="BR5" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="BS5">
         <v>-1.3</v>
@@ -4094,7 +4097,7 @@
         <v>5.7</v>
       </c>
       <c r="CO5" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="CP5">
         <v>-1.5</v>
@@ -4163,7 +4166,7 @@
         <v>7.4</v>
       </c>
       <c r="DL5" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="DM5">
         <v>-2.3</v>
@@ -4232,7 +4235,7 @@
         <v>4.1</v>
       </c>
       <c r="EI5" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="EJ5">
         <v>-1.9</v>
@@ -4303,10 +4306,10 @@
         <v>225</v>
       </c>
       <c r="H6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="I6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="J6" t="s">
         <v>246</v>
@@ -4318,10 +4321,10 @@
         <v>56.3</v>
       </c>
       <c r="M6" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="N6" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="O6">
         <v>3</v>
@@ -4345,10 +4348,10 @@
         <v>1.018</v>
       </c>
       <c r="V6" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="W6">
-        <v>28.1</v>
+        <v>30.1</v>
       </c>
       <c r="X6">
         <v>5</v>
@@ -4375,7 +4378,7 @@
         <v>293</v>
       </c>
       <c r="AF6">
-        <v>11.4</v>
+        <v>11.3</v>
       </c>
       <c r="AG6" t="s">
         <v>297</v>
@@ -4411,7 +4414,7 @@
         <v>321</v>
       </c>
       <c r="AR6" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AS6">
         <v>0.82</v>
@@ -4489,7 +4492,7 @@
         <v>11</v>
       </c>
       <c r="BR6" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="BS6">
         <v>5.3</v>
@@ -4558,7 +4561,7 @@
         <v>12</v>
       </c>
       <c r="CO6" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="CP6">
         <v>6.2</v>
@@ -4627,7 +4630,7 @@
         <v>13.9</v>
       </c>
       <c r="DL6" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="DM6">
         <v>6.8</v>
@@ -4696,7 +4699,7 @@
         <v>15.7</v>
       </c>
       <c r="EI6" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="EJ6">
         <v>7.1</v>
@@ -4767,10 +4770,10 @@
         <v>226</v>
       </c>
       <c r="H7" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="I7" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="J7" t="s">
         <v>247</v>
@@ -4782,10 +4785,10 @@
         <v>55</v>
       </c>
       <c r="M7" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="N7" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="O7">
         <v>3</v>
@@ -4809,10 +4812,10 @@
         <v>1.014</v>
       </c>
       <c r="V7" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="W7">
-        <v>151.5</v>
+        <v>153.5</v>
       </c>
       <c r="X7">
         <v>5</v>
@@ -4875,7 +4878,7 @@
         <v>322</v>
       </c>
       <c r="AR7" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AS7">
         <v>0.92</v>
@@ -4953,7 +4956,7 @@
         <v>12.6</v>
       </c>
       <c r="BR7" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="BS7">
         <v>-1</v>
@@ -5022,7 +5025,7 @@
         <v>11.2</v>
       </c>
       <c r="CO7" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="CP7">
         <v>-4.2</v>
@@ -5091,7 +5094,7 @@
         <v>9.699999999999999</v>
       </c>
       <c r="DL7" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="DM7">
         <v>-4</v>
@@ -5160,7 +5163,7 @@
         <v>9.6</v>
       </c>
       <c r="EI7" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="EJ7">
         <v>-4.3</v>
@@ -5231,10 +5234,10 @@
         <v>227</v>
       </c>
       <c r="H8" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="I8" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="J8" t="s">
         <v>248</v>
@@ -5246,10 +5249,10 @@
         <v>54.9</v>
       </c>
       <c r="M8" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="N8" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="O8">
         <v>3</v>
@@ -5276,7 +5279,7 @@
         <v>282</v>
       </c>
       <c r="W8">
-        <v>39.6</v>
+        <v>41.6</v>
       </c>
       <c r="X8">
         <v>5</v>
@@ -5336,10 +5339,10 @@
         <v>312</v>
       </c>
       <c r="AQ8" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AR8" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AS8">
         <v>0.92</v>
@@ -5417,7 +5420,7 @@
         <v>11.5</v>
       </c>
       <c r="BR8" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="BS8">
         <v>-2.3</v>
@@ -5486,7 +5489,7 @@
         <v>10.7</v>
       </c>
       <c r="CO8" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="CP8">
         <v>-2.2</v>
@@ -5555,7 +5558,7 @@
         <v>9.300000000000001</v>
       </c>
       <c r="DL8" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="DM8">
         <v>-1.9</v>
@@ -5624,7 +5627,7 @@
         <v>7.9</v>
       </c>
       <c r="EI8" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="EJ8">
         <v>-1.6</v>
@@ -5695,10 +5698,10 @@
         <v>228</v>
       </c>
       <c r="H9" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="I9" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="J9" t="s">
         <v>249</v>
@@ -5710,10 +5713,10 @@
         <v>54.4</v>
       </c>
       <c r="M9" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="N9" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="O9">
         <v>2</v>
@@ -5740,7 +5743,7 @@
         <v>283</v>
       </c>
       <c r="W9">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="X9">
         <v>5</v>
@@ -5800,10 +5803,10 @@
         <v>313</v>
       </c>
       <c r="AQ9" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AR9" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AS9">
         <v>0.92</v>
@@ -5881,7 +5884,7 @@
         <v>8.9</v>
       </c>
       <c r="BR9" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="BS9">
         <v>0</v>
@@ -5950,7 +5953,7 @@
         <v>12.6</v>
       </c>
       <c r="CO9" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="CP9">
         <v>0</v>
@@ -6019,7 +6022,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="DL9" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="DM9">
         <v>0</v>
@@ -6088,7 +6091,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="EI9" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="EJ9">
         <v>0</v>
@@ -6159,10 +6162,10 @@
         <v>229</v>
       </c>
       <c r="H10" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="I10" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="J10" t="s">
         <v>250</v>
@@ -6174,10 +6177,10 @@
         <v>54.5</v>
       </c>
       <c r="M10" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="N10" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="O10">
         <v>2</v>
@@ -6204,7 +6207,7 @@
         <v>284</v>
       </c>
       <c r="W10">
-        <v>37.7</v>
+        <v>39.7</v>
       </c>
       <c r="X10">
         <v>5</v>
@@ -6264,10 +6267,10 @@
         <v>311</v>
       </c>
       <c r="AQ10" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AR10" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AS10">
         <v>0.92</v>
@@ -6345,7 +6348,7 @@
         <v>12.5</v>
       </c>
       <c r="BR10" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="BS10">
         <v>-0</v>
@@ -6414,7 +6417,7 @@
         <v>13.1</v>
       </c>
       <c r="CO10" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="CP10">
         <v>-0</v>
@@ -6483,7 +6486,7 @@
         <v>11.6</v>
       </c>
       <c r="DL10" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="DM10">
         <v>-0</v>
@@ -6552,7 +6555,7 @@
         <v>11.3</v>
       </c>
       <c r="EI10" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="EJ10">
         <v>-3.9</v>
@@ -6623,10 +6626,10 @@
         <v>230</v>
       </c>
       <c r="H11" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="I11" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="J11" t="s">
         <v>251</v>
@@ -6638,10 +6641,10 @@
         <v>41.8</v>
       </c>
       <c r="M11" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="N11" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="O11">
         <v>-5</v>
@@ -6668,7 +6671,7 @@
         <v>285</v>
       </c>
       <c r="W11">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="X11">
         <v>5</v>
@@ -6728,10 +6731,10 @@
         <v>312</v>
       </c>
       <c r="AQ11" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AR11" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AS11">
         <v>0.92</v>
@@ -6809,7 +6812,7 @@
         <v>16</v>
       </c>
       <c r="BR11" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="BS11">
         <v>-8.5</v>
@@ -6878,7 +6881,7 @@
         <v>14.7</v>
       </c>
       <c r="CO11" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="CP11">
         <v>-7.8</v>
@@ -6947,7 +6950,7 @@
         <v>14.9</v>
       </c>
       <c r="DL11" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="DM11">
         <v>-7.8</v>
@@ -7016,7 +7019,7 @@
         <v>17.4</v>
       </c>
       <c r="EI11" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="EJ11">
         <v>-7.4</v>
@@ -7087,10 +7090,10 @@
         <v>231</v>
       </c>
       <c r="H12" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="I12" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="J12" t="s">
         <v>252</v>
@@ -7102,10 +7105,10 @@
         <v>46.2</v>
       </c>
       <c r="M12" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="N12" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="O12">
         <v>-2</v>
@@ -7132,7 +7135,7 @@
         <v>286</v>
       </c>
       <c r="W12">
-        <v>151.6</v>
+        <v>153.6</v>
       </c>
       <c r="X12">
         <v>5</v>
@@ -7192,10 +7195,10 @@
         <v>314</v>
       </c>
       <c r="AQ12" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AR12" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AS12">
         <v>0.92</v>
@@ -7273,7 +7276,7 @@
         <v>16.5</v>
       </c>
       <c r="BR12" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="BS12">
         <v>-6.2</v>
@@ -7342,7 +7345,7 @@
         <v>13</v>
       </c>
       <c r="CO12" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="CP12">
         <v>-4.5</v>
@@ -7411,7 +7414,7 @@
         <v>14.2</v>
       </c>
       <c r="DL12" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="DM12">
         <v>-3.6</v>
@@ -7480,7 +7483,7 @@
         <v>10.6</v>
       </c>
       <c r="EI12" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="EJ12">
         <v>-2.4</v>
@@ -7566,10 +7569,10 @@
         <v>54.9</v>
       </c>
       <c r="M13" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="N13" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="O13">
         <v>3</v>
@@ -7596,7 +7599,7 @@
         <v>287</v>
       </c>
       <c r="W13">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="X13">
         <v>5</v>
@@ -7656,10 +7659,10 @@
         <v>315</v>
       </c>
       <c r="AQ13" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AR13" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AS13">
         <v>0.92</v>
@@ -7737,7 +7740,7 @@
         <v>16.2</v>
       </c>
       <c r="BR13" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="BS13">
         <v>0</v>
@@ -7806,7 +7809,7 @@
         <v>17</v>
       </c>
       <c r="CO13" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="CP13">
         <v>0</v>
@@ -7875,7 +7878,7 @@
         <v>17.4</v>
       </c>
       <c r="DL13" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="DM13">
         <v>0</v>
@@ -7944,7 +7947,7 @@
         <v>17.9</v>
       </c>
       <c r="EI13" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="EJ13">
         <v>0</v>
@@ -8015,10 +8018,10 @@
         <v>233</v>
       </c>
       <c r="H14" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="I14" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="J14" t="s">
         <v>254</v>
@@ -8030,10 +8033,10 @@
         <v>57.2</v>
       </c>
       <c r="M14" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="N14" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="O14">
         <v>4</v>
@@ -8060,7 +8063,7 @@
         <v>288</v>
       </c>
       <c r="W14">
-        <v>54</v>
+        <v>56.1</v>
       </c>
       <c r="X14">
         <v>5</v>
@@ -8120,10 +8123,10 @@
         <v>312</v>
       </c>
       <c r="AQ14" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AR14" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AS14">
         <v>1</v>
@@ -8201,7 +8204,7 @@
         <v>7.4</v>
       </c>
       <c r="BR14" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="BS14">
         <v>-2.8</v>
@@ -8270,7 +8273,7 @@
         <v>6.8</v>
       </c>
       <c r="CO14" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="CP14">
         <v>-1.7</v>
@@ -8339,7 +8342,7 @@
         <v>4.9</v>
       </c>
       <c r="DL14" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="DM14">
         <v>-1.6</v>
@@ -8408,7 +8411,7 @@
         <v>5.4</v>
       </c>
       <c r="EI14" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="EJ14">
         <v>-2.2</v>
@@ -8479,10 +8482,10 @@
         <v>234</v>
       </c>
       <c r="H15" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="I15" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="J15" t="s">
         <v>255</v>
@@ -8494,10 +8497,10 @@
         <v>47.2</v>
       </c>
       <c r="M15" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="N15" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="O15">
         <v>-2</v>
@@ -8524,7 +8527,7 @@
         <v>289</v>
       </c>
       <c r="W15">
-        <v>52.8</v>
+        <v>54.8</v>
       </c>
       <c r="X15">
         <v>5</v>
@@ -8584,10 +8587,10 @@
         <v>316</v>
       </c>
       <c r="AQ15" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AR15" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AS15">
         <v>0.92</v>
@@ -8665,7 +8668,7 @@
         <v>13.2</v>
       </c>
       <c r="BR15" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="BS15">
         <v>-5.9</v>
@@ -8734,7 +8737,7 @@
         <v>13.3</v>
       </c>
       <c r="CO15" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="CP15">
         <v>-5.6</v>
@@ -8803,7 +8806,7 @@
         <v>13.8</v>
       </c>
       <c r="DL15" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="DM15">
         <v>-4.9</v>
@@ -8872,7 +8875,7 @@
         <v>11</v>
       </c>
       <c r="EI15" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="EJ15">
         <v>-4.2</v>
@@ -8943,13 +8946,13 @@
         <v>235</v>
       </c>
       <c r="H16" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="I16" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="J16" t="s">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="K16">
         <v>56.8</v>
@@ -8958,10 +8961,10 @@
         <v>56.3</v>
       </c>
       <c r="M16" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="N16" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="O16">
         <v>3</v>
@@ -8988,7 +8991,7 @@
         <v>290</v>
       </c>
       <c r="W16">
-        <v>148.5</v>
+        <v>150.5</v>
       </c>
       <c r="X16">
         <v>5</v>
@@ -9048,10 +9051,10 @@
         <v>310</v>
       </c>
       <c r="AQ16" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AR16" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AS16">
         <v>0.86</v>
@@ -9336,7 +9339,7 @@
         <v>5.3</v>
       </c>
       <c r="EI16" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="EJ16">
         <v>0.1</v>
@@ -9413,7 +9416,7 @@
         <v>238</v>
       </c>
       <c r="J17" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="K17">
         <v>72.90000000000001</v>
@@ -9422,10 +9425,10 @@
         <v>70.3</v>
       </c>
       <c r="M17" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="N17" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="O17">
         <v>11</v>
@@ -9452,7 +9455,7 @@
         <v>291</v>
       </c>
       <c r="W17">
-        <v>96.8</v>
+        <v>98.8</v>
       </c>
       <c r="X17">
         <v>5</v>
@@ -9512,10 +9515,10 @@
         <v>310</v>
       </c>
       <c r="AQ17" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AR17" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AS17">
         <v>0.78</v>
@@ -9593,7 +9596,7 @@
         <v>10.1</v>
       </c>
       <c r="BR17" t="s">
-        <v>347</v>
+        <v>357</v>
       </c>
       <c r="BS17">
         <v>4.3</v>
@@ -9662,7 +9665,7 @@
         <v>7.7</v>
       </c>
       <c r="CO17" t="s">
-        <v>347</v>
+        <v>357</v>
       </c>
       <c r="CP17">
         <v>3.6</v>
@@ -9731,7 +9734,7 @@
         <v>6.3</v>
       </c>
       <c r="DL17" t="s">
-        <v>347</v>
+        <v>357</v>
       </c>
       <c r="DM17">
         <v>3.4</v>
@@ -9800,7 +9803,7 @@
         <v>5.2</v>
       </c>
       <c r="EI17" t="s">
-        <v>347</v>
+        <v>357</v>
       </c>
       <c r="EJ17">
         <v>3.2</v>
@@ -9956,10 +9959,10 @@
         <v>6</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="G1" s="3" t="s">
         <v>42</v>
@@ -9974,28 +9977,28 @@
         <v>22</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L1" s="3" t="s">
         <v>23</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="N1" s="3" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="P1" s="3" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q1" s="3" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="R1" s="3" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="S1" s="3" t="s">
         <v>44</v>
@@ -10007,109 +10010,109 @@
         <v>46</v>
       </c>
       <c r="V1" s="3" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="W1" s="3" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="X1" s="3" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Y1" s="3" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Z1" s="3" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AA1" s="3" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AB1" s="3" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AC1" s="3" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AD1" s="3" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AE1" s="3" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AF1" s="3" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AG1" s="3" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AH1" s="3" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI1" s="3" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AJ1" s="3" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AK1" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AL1" s="3" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AM1" s="3" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AN1" s="3" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AO1" s="3" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AP1" s="3" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AQ1" s="3" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AR1" s="3" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AS1" s="3" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AT1" s="3" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AU1" s="3" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AV1" s="3" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AW1" s="3" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AX1" s="3" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AY1" s="3" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AZ1" s="3" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="BA1" s="3" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="BB1" s="3" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="BC1" s="3" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="BD1" s="3" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="BE1" s="3" t="s">
         <v>31</v>
@@ -10118,16 +10121,16 @@
         <v>30</v>
       </c>
       <c r="BG1" s="3" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="BH1" s="3" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="BI1" s="3" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="BJ1" s="3" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="2" spans="1:62">
@@ -10144,7 +10147,7 @@
         <v>222</v>
       </c>
       <c r="E2" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="F2" t="s">
         <v>210</v>
@@ -10153,13 +10156,13 @@
         <v>317</v>
       </c>
       <c r="H2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="I2" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="J2">
-        <v>152.9</v>
+        <v>154.9</v>
       </c>
       <c r="K2">
         <v>0</v>
@@ -10240,7 +10243,7 @@
         <v>5</v>
       </c>
       <c r="AK2" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -10261,7 +10264,7 @@
         <v>1.1331</v>
       </c>
       <c r="AR2" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AS2">
         <v>2346</v>
@@ -10332,22 +10335,22 @@
         <v>222</v>
       </c>
       <c r="E3" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="F3" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="G3" t="s">
         <v>317</v>
       </c>
       <c r="H3" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="I3" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="J3">
-        <v>152.9</v>
+        <v>154.9</v>
       </c>
       <c r="K3">
         <v>0</v>
@@ -10428,7 +10431,7 @@
         <v>5.2</v>
       </c>
       <c r="AK3" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -10449,7 +10452,7 @@
         <v>1.1318</v>
       </c>
       <c r="AR3" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AS3">
         <v>2387</v>
@@ -10520,22 +10523,22 @@
         <v>222</v>
       </c>
       <c r="E4" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="F4" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="G4" t="s">
         <v>317</v>
       </c>
       <c r="H4" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="I4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="J4">
-        <v>152.9</v>
+        <v>154.9</v>
       </c>
       <c r="K4">
         <v>0</v>
@@ -10616,7 +10619,7 @@
         <v>5.1</v>
       </c>
       <c r="AK4" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -10637,7 +10640,7 @@
         <v>1.1302</v>
       </c>
       <c r="AR4" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AS4">
         <v>2437</v>
@@ -10708,22 +10711,22 @@
         <v>222</v>
       </c>
       <c r="E5" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="F5" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="G5" t="s">
         <v>317</v>
       </c>
       <c r="H5" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="I5" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="J5">
-        <v>152.9</v>
+        <v>154.9</v>
       </c>
       <c r="K5">
         <v>0</v>
@@ -10804,7 +10807,7 @@
         <v>5.7</v>
       </c>
       <c r="AK5" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -10825,7 +10828,7 @@
         <v>1.129</v>
       </c>
       <c r="AR5" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AS5">
         <v>2477</v>
@@ -10896,7 +10899,7 @@
         <v>223</v>
       </c>
       <c r="E6" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="F6" t="s">
         <v>211</v>
@@ -10905,13 +10908,13 @@
         <v>318</v>
       </c>
       <c r="H6" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="I6" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="J6">
-        <v>10.2</v>
+        <v>109.8</v>
       </c>
       <c r="K6">
         <v>0</v>
@@ -10932,10 +10935,10 @@
         <v>9.5</v>
       </c>
       <c r="Q6">
-        <v>92.7</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="R6">
-        <v>78.90000000000001</v>
+        <v>78.5</v>
       </c>
       <c r="S6">
         <v>0.92</v>
@@ -10953,16 +10956,16 @@
         <v>311</v>
       </c>
       <c r="X6">
-        <v>88.40000000000001</v>
+        <v>88</v>
       </c>
       <c r="Y6">
         <v>95.5</v>
       </c>
       <c r="Z6">
-        <v>68.7</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="AA6">
-        <v>52.7</v>
+        <v>51.9</v>
       </c>
       <c r="AB6">
         <v>988.2</v>
@@ -10974,7 +10977,7 @@
         <v>35</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AF6">
         <v>0</v>
@@ -10986,37 +10989,37 @@
         <v>1688</v>
       </c>
       <c r="AI6">
-        <v>5.7</v>
+        <v>7.3</v>
       </c>
       <c r="AJ6">
         <v>10.8</v>
       </c>
       <c r="AK6" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AL6">
-        <v>191.4</v>
+        <v>180</v>
       </c>
       <c r="AM6">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="AN6">
-        <v>5.7</v>
+        <v>7.2</v>
       </c>
       <c r="AO6">
-        <v>2.1</v>
+        <v>1.3</v>
       </c>
       <c r="AP6">
-        <v>-3.2</v>
+        <v>-5.2</v>
       </c>
       <c r="AQ6">
-        <v>1.1203</v>
+        <v>1.1214</v>
       </c>
       <c r="AR6" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AS6">
-        <v>2792</v>
+        <v>2764</v>
       </c>
       <c r="AT6" t="s">
         <v>297</v>
@@ -11025,46 +11028,46 @@
         <v>300</v>
       </c>
       <c r="AV6">
-        <v>81.2</v>
+        <v>81.8</v>
       </c>
       <c r="AW6">
-        <v>1.075</v>
+        <v>1.076</v>
       </c>
       <c r="AX6">
-        <v>78.8</v>
+        <v>78.3</v>
       </c>
       <c r="AY6">
-        <v>82.09999999999999</v>
+        <v>83.7</v>
       </c>
       <c r="AZ6">
-        <v>58</v>
+        <v>59.3</v>
       </c>
       <c r="BA6">
-        <v>57.6</v>
+        <v>57.7</v>
       </c>
       <c r="BB6">
-        <v>51.4</v>
+        <v>52.4</v>
       </c>
       <c r="BC6">
-        <v>12</v>
+        <v>14.6</v>
       </c>
       <c r="BD6" t="s">
         <v>293</v>
       </c>
       <c r="BE6">
-        <v>5.6</v>
+        <v>11.1</v>
       </c>
       <c r="BF6" t="s">
         <v>293</v>
       </c>
       <c r="BG6">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="BH6">
         <v>87.2</v>
       </c>
       <c r="BI6">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BJ6">
         <v>6.2</v>
@@ -11084,22 +11087,22 @@
         <v>223</v>
       </c>
       <c r="E7" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="F7" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="G7" t="s">
         <v>318</v>
       </c>
       <c r="H7" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="I7" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="J7">
-        <v>10.2</v>
+        <v>109.8</v>
       </c>
       <c r="K7">
         <v>0</v>
@@ -11120,10 +11123,10 @@
         <v>10.5</v>
       </c>
       <c r="Q7">
-        <v>94.09999999999999</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="R7">
-        <v>79.8</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="S7">
         <v>0.92</v>
@@ -11138,19 +11141,19 @@
         <v>0</v>
       </c>
       <c r="W7" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="X7">
-        <v>89.40000000000001</v>
+        <v>89</v>
       </c>
       <c r="Y7">
         <v>96.3</v>
       </c>
       <c r="Z7">
-        <v>67.2</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="AA7">
-        <v>48.6</v>
+        <v>47.8</v>
       </c>
       <c r="AB7">
         <v>988.1</v>
@@ -11162,7 +11165,7 @@
         <v>28.8</v>
       </c>
       <c r="AE7">
-        <v>1.3</v>
+        <v>4.8</v>
       </c>
       <c r="AF7">
         <v>0.002</v>
@@ -11174,37 +11177,37 @@
         <v>1161</v>
       </c>
       <c r="AI7">
-        <v>5.8</v>
+        <v>7.3</v>
       </c>
       <c r="AJ7">
         <v>10.7</v>
       </c>
       <c r="AK7" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="AL7">
-        <v>189.5</v>
+        <v>180</v>
       </c>
       <c r="AM7">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="AN7">
-        <v>5.8</v>
+        <v>7.2</v>
       </c>
       <c r="AO7">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="AP7">
-        <v>-3.4</v>
+        <v>-5.2</v>
       </c>
       <c r="AQ7">
-        <v>1.1186</v>
+        <v>1.1197</v>
       </c>
       <c r="AR7" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AS7">
-        <v>2863</v>
+        <v>2836</v>
       </c>
       <c r="AT7" t="s">
         <v>297</v>
@@ -11213,46 +11216,46 @@
         <v>300</v>
       </c>
       <c r="AV7">
-        <v>81.59999999999999</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="AW7">
-        <v>1.076</v>
+        <v>1.078</v>
       </c>
       <c r="AX7">
-        <v>79.09999999999999</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="AY7">
-        <v>82.59999999999999</v>
+        <v>84.3</v>
       </c>
       <c r="AZ7">
-        <v>58.3</v>
+        <v>59.5</v>
       </c>
       <c r="BA7">
-        <v>57.6</v>
+        <v>57.7</v>
       </c>
       <c r="BB7">
-        <v>51.7</v>
+        <v>52.7</v>
       </c>
       <c r="BC7">
-        <v>13.1</v>
+        <v>15</v>
       </c>
       <c r="BD7" t="s">
         <v>293</v>
       </c>
       <c r="BE7">
-        <v>2.1</v>
+        <v>7.5</v>
       </c>
       <c r="BF7" t="s">
         <v>293</v>
       </c>
       <c r="BG7">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="BH7">
         <v>89</v>
       </c>
       <c r="BI7">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BJ7">
         <v>6.3</v>
@@ -11272,22 +11275,22 @@
         <v>223</v>
       </c>
       <c r="E8" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="F8" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="G8" t="s">
         <v>318</v>
       </c>
       <c r="H8" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="I8" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="J8">
-        <v>10.2</v>
+        <v>109.8</v>
       </c>
       <c r="K8">
         <v>0</v>
@@ -11308,10 +11311,10 @@
         <v>9.9</v>
       </c>
       <c r="Q8">
-        <v>95.40000000000001</v>
+        <v>90.2</v>
       </c>
       <c r="R8">
-        <v>80.40000000000001</v>
+        <v>79.5</v>
       </c>
       <c r="S8">
         <v>0.92</v>
@@ -11326,19 +11329,19 @@
         <v>0</v>
       </c>
       <c r="W8" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="X8">
-        <v>89.90000000000001</v>
+        <v>89.5</v>
       </c>
       <c r="Y8">
         <v>97.2</v>
       </c>
       <c r="Z8">
-        <v>67.09999999999999</v>
+        <v>66.5</v>
       </c>
       <c r="AA8">
-        <v>47.8</v>
+        <v>46.9</v>
       </c>
       <c r="AB8">
         <v>987.5</v>
@@ -11350,7 +11353,7 @@
         <v>20.6</v>
       </c>
       <c r="AE8">
-        <v>1.8</v>
+        <v>4.8</v>
       </c>
       <c r="AF8">
         <v>0.002</v>
@@ -11362,37 +11365,37 @@
         <v>1492</v>
       </c>
       <c r="AI8">
-        <v>5.5</v>
+        <v>7.2</v>
       </c>
       <c r="AJ8">
         <v>10.7</v>
       </c>
       <c r="AK8" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AL8">
-        <v>191.3</v>
+        <v>180</v>
       </c>
       <c r="AM8">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="AN8">
-        <v>5.5</v>
+        <v>7.1</v>
       </c>
       <c r="AO8">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="AP8">
-        <v>-3.1</v>
+        <v>-5.1</v>
       </c>
       <c r="AQ8">
-        <v>1.117</v>
+        <v>1.118</v>
       </c>
       <c r="AR8" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AS8">
-        <v>2918</v>
+        <v>2890</v>
       </c>
       <c r="AT8" t="s">
         <v>297</v>
@@ -11401,46 +11404,46 @@
         <v>300</v>
       </c>
       <c r="AV8">
-        <v>81.8</v>
+        <v>82.7</v>
       </c>
       <c r="AW8">
-        <v>1.076</v>
+        <v>1.078</v>
       </c>
       <c r="AX8">
-        <v>79.5</v>
+        <v>79.2</v>
       </c>
       <c r="AY8">
-        <v>82.7</v>
+        <v>84.5</v>
       </c>
       <c r="AZ8">
-        <v>58.1</v>
+        <v>59.5</v>
       </c>
       <c r="BA8">
-        <v>57.7</v>
+        <v>57.8</v>
       </c>
       <c r="BB8">
-        <v>51.2</v>
+        <v>52.2</v>
       </c>
       <c r="BC8">
-        <v>13.7</v>
+        <v>15.4</v>
       </c>
       <c r="BD8" t="s">
         <v>293</v>
       </c>
       <c r="BE8">
-        <v>0.3</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF8" t="s">
         <v>293</v>
       </c>
       <c r="BG8">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="BH8">
         <v>89.90000000000001</v>
       </c>
       <c r="BI8">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BJ8">
         <v>6</v>
@@ -11460,25 +11463,25 @@
         <v>223</v>
       </c>
       <c r="E9" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="F9" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="G9" t="s">
         <v>318</v>
       </c>
       <c r="H9" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="I9" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="J9">
-        <v>10.2</v>
+        <v>109.8</v>
       </c>
       <c r="K9">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="L9">
         <v>5</v>
@@ -11496,10 +11499,10 @@
         <v>13</v>
       </c>
       <c r="Q9">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="R9">
-        <v>77.40000000000001</v>
+        <v>79.2</v>
       </c>
       <c r="S9">
         <v>0.92</v>
@@ -11514,7 +11517,7 @@
         <v>0</v>
       </c>
       <c r="W9" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="X9">
         <v>90.2</v>
@@ -11523,10 +11526,10 @@
         <v>97.2</v>
       </c>
       <c r="Z9">
-        <v>67.09999999999999</v>
+        <v>66.5</v>
       </c>
       <c r="AA9">
-        <v>47.4</v>
+        <v>46.1</v>
       </c>
       <c r="AB9">
         <v>987.4</v>
@@ -11538,7 +11541,7 @@
         <v>30.7</v>
       </c>
       <c r="AE9">
-        <v>2.3</v>
+        <v>5</v>
       </c>
       <c r="AF9">
         <v>0.003</v>
@@ -11550,34 +11553,34 @@
         <v>1584</v>
       </c>
       <c r="AI9">
-        <v>4.9</v>
+        <v>7</v>
       </c>
       <c r="AJ9">
         <v>10.5</v>
       </c>
       <c r="AK9" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="AL9">
         <v>180</v>
       </c>
       <c r="AM9">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="AN9">
-        <v>4.9</v>
+        <v>6.9</v>
       </c>
       <c r="AO9">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="AP9">
-        <v>-3.5</v>
+        <v>-5</v>
       </c>
       <c r="AQ9">
-        <v>1.1162</v>
+        <v>1.1164</v>
       </c>
       <c r="AR9" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AS9">
         <v>2941</v>
@@ -11589,34 +11592,34 @@
         <v>300</v>
       </c>
       <c r="AV9">
+        <v>82.7</v>
+      </c>
+      <c r="AW9">
+        <v>1.079</v>
+      </c>
+      <c r="AX9">
         <v>79.40000000000001</v>
       </c>
-      <c r="AW9">
-        <v>1.071</v>
-      </c>
-      <c r="AX9">
-        <v>77</v>
-      </c>
       <c r="AY9">
-        <v>80.7</v>
+        <v>84.5</v>
       </c>
       <c r="AZ9">
-        <v>57.8</v>
+        <v>59.5</v>
       </c>
       <c r="BA9">
-        <v>57.2</v>
+        <v>57.9</v>
       </c>
       <c r="BB9">
-        <v>50.9</v>
+        <v>51.4</v>
       </c>
       <c r="BC9">
-        <v>14.3</v>
+        <v>15.8</v>
       </c>
       <c r="BD9" t="s">
         <v>293</v>
       </c>
       <c r="BE9">
-        <v>2.1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="BF9" t="s">
         <v>293</v>
@@ -11628,7 +11631,7 @@
         <v>90.3</v>
       </c>
       <c r="BI9">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="BJ9">
         <v>5.7</v>
@@ -11648,7 +11651,7 @@
         <v>224</v>
       </c>
       <c r="E10" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="F10" t="s">
         <v>211</v>
@@ -11657,13 +11660,13 @@
         <v>319</v>
       </c>
       <c r="H10" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="I10" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="J10">
-        <v>3.2</v>
+        <v>5.2</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -11744,7 +11747,7 @@
         <v>17.2</v>
       </c>
       <c r="AK10" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AL10">
         <v>22.5</v>
@@ -11765,7 +11768,7 @@
         <v>1.1542</v>
       </c>
       <c r="AR10" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AS10">
         <v>1744</v>
@@ -11836,22 +11839,22 @@
         <v>224</v>
       </c>
       <c r="E11" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="F11" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="G11" t="s">
         <v>319</v>
       </c>
       <c r="H11" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="I11" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="J11">
-        <v>3.2</v>
+        <v>5.2</v>
       </c>
       <c r="K11">
         <v>0</v>
@@ -11932,7 +11935,7 @@
         <v>17.7</v>
       </c>
       <c r="AK11" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AL11">
         <v>22.5</v>
@@ -11953,7 +11956,7 @@
         <v>1.1541</v>
       </c>
       <c r="AR11" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AS11">
         <v>1752</v>
@@ -12024,22 +12027,22 @@
         <v>224</v>
       </c>
       <c r="E12" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="F12" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="G12" t="s">
         <v>319</v>
       </c>
       <c r="H12" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="I12" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="J12">
-        <v>3.2</v>
+        <v>5.2</v>
       </c>
       <c r="K12">
         <v>0</v>
@@ -12120,7 +12123,7 @@
         <v>18.9</v>
       </c>
       <c r="AK12" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AL12">
         <v>22.5</v>
@@ -12141,7 +12144,7 @@
         <v>1.154</v>
       </c>
       <c r="AR12" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AS12">
         <v>1776</v>
@@ -12212,25 +12215,25 @@
         <v>224</v>
       </c>
       <c r="E13" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="F13" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="G13" t="s">
         <v>319</v>
       </c>
       <c r="H13" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="I13" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="J13">
-        <v>3.2</v>
+        <v>5.2</v>
       </c>
       <c r="K13">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="L13">
         <v>5</v>
@@ -12308,7 +12311,7 @@
         <v>17.9</v>
       </c>
       <c r="AK13" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AL13">
         <v>22.5</v>
@@ -12329,7 +12332,7 @@
         <v>1.154</v>
       </c>
       <c r="AR13" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AS13">
         <v>1784</v>
@@ -12400,7 +12403,7 @@
         <v>222</v>
       </c>
       <c r="E14" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="F14" t="s">
         <v>212</v>
@@ -12409,13 +12412,13 @@
         <v>320</v>
       </c>
       <c r="H14" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="I14" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="J14">
-        <v>152.9</v>
+        <v>154.9</v>
       </c>
       <c r="K14">
         <v>0</v>
@@ -12496,7 +12499,7 @@
         <v>5.9</v>
       </c>
       <c r="AK14" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -12517,7 +12520,7 @@
         <v>1.1293</v>
       </c>
       <c r="AR14" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AS14">
         <v>2476</v>
@@ -12588,25 +12591,25 @@
         <v>222</v>
       </c>
       <c r="E15" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="F15" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="G15" t="s">
         <v>320</v>
       </c>
       <c r="H15" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="I15" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="J15">
-        <v>152.9</v>
+        <v>154.9</v>
       </c>
       <c r="K15">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="L15">
         <v>5</v>
@@ -12684,7 +12687,7 @@
         <v>5.7</v>
       </c>
       <c r="AK15" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -12705,7 +12708,7 @@
         <v>1.1291</v>
       </c>
       <c r="AR15" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AS15">
         <v>2487</v>
@@ -12776,25 +12779,25 @@
         <v>222</v>
       </c>
       <c r="E16" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="F16" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="G16" t="s">
         <v>320</v>
       </c>
       <c r="H16" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="I16" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="J16">
-        <v>152.9</v>
+        <v>154.9</v>
       </c>
       <c r="K16">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="L16">
         <v>5</v>
@@ -12830,7 +12833,7 @@
         <v>0</v>
       </c>
       <c r="W16" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="X16">
         <v>80.90000000000001</v>
@@ -12872,7 +12875,7 @@
         <v>7.4</v>
       </c>
       <c r="AK16" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -12893,7 +12896,7 @@
         <v>1.1302</v>
       </c>
       <c r="AR16" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AS16">
         <v>2445</v>
@@ -12964,7 +12967,7 @@
         <v>222</v>
       </c>
       <c r="E17" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="F17" t="s">
         <v>216</v>
@@ -12973,16 +12976,16 @@
         <v>320</v>
       </c>
       <c r="H17" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="I17" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="J17">
-        <v>152.9</v>
+        <v>154.9</v>
       </c>
       <c r="K17">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="L17">
         <v>5</v>
@@ -13018,7 +13021,7 @@
         <v>0</v>
       </c>
       <c r="W17" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="X17">
         <v>79.09999999999999</v>
@@ -13060,7 +13063,7 @@
         <v>4.1</v>
       </c>
       <c r="AK17" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AL17">
         <v>45</v>
@@ -13081,7 +13084,7 @@
         <v>1.1343</v>
       </c>
       <c r="AR17" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AS17">
         <v>2323</v>
@@ -13152,7 +13155,7 @@
         <v>225</v>
       </c>
       <c r="E18" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="F18" t="s">
         <v>213</v>
@@ -13161,13 +13164,13 @@
         <v>321</v>
       </c>
       <c r="H18" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="I18" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="J18">
-        <v>28.1</v>
+        <v>30.1</v>
       </c>
       <c r="K18">
         <v>0</v>
@@ -13248,7 +13251,7 @@
         <v>11</v>
       </c>
       <c r="AK18" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AL18">
         <v>247.5</v>
@@ -13269,7 +13272,7 @@
         <v>1.2197</v>
       </c>
       <c r="AR18" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AS18">
         <v>-28</v>
@@ -13340,25 +13343,25 @@
         <v>225</v>
       </c>
       <c r="E19" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="F19" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="G19" t="s">
         <v>321</v>
       </c>
       <c r="H19" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="I19" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="J19">
-        <v>28.1</v>
+        <v>30.1</v>
       </c>
       <c r="K19">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="L19">
         <v>5</v>
@@ -13436,7 +13439,7 @@
         <v>12</v>
       </c>
       <c r="AK19" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AL19">
         <v>247.5</v>
@@ -13457,7 +13460,7 @@
         <v>1.2177</v>
       </c>
       <c r="AR19" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AS19">
         <v>32</v>
@@ -13528,25 +13531,25 @@
         <v>225</v>
       </c>
       <c r="E20" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="F20" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="G20" t="s">
         <v>321</v>
       </c>
       <c r="H20" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="I20" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="J20">
-        <v>28.1</v>
+        <v>30.1</v>
       </c>
       <c r="K20">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="L20">
         <v>5</v>
@@ -13624,7 +13627,7 @@
         <v>13.9</v>
       </c>
       <c r="AK20" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AL20">
         <v>247.5</v>
@@ -13645,7 +13648,7 @@
         <v>1.216</v>
       </c>
       <c r="AR20" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AS20">
         <v>80</v>
@@ -13684,7 +13687,7 @@
         <v>293</v>
       </c>
       <c r="BE20">
-        <v>11.4</v>
+        <v>11.3</v>
       </c>
       <c r="BF20" t="s">
         <v>293</v>
@@ -13716,25 +13719,25 @@
         <v>225</v>
       </c>
       <c r="E21" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="F21" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="G21" t="s">
         <v>321</v>
       </c>
       <c r="H21" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="I21" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="J21">
-        <v>28.1</v>
+        <v>30.1</v>
       </c>
       <c r="K21">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="L21">
         <v>5</v>
@@ -13812,7 +13815,7 @@
         <v>15.7</v>
       </c>
       <c r="AK21" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AL21">
         <v>247.5</v>
@@ -13833,7 +13836,7 @@
         <v>1.2166</v>
       </c>
       <c r="AR21" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AS21">
         <v>64</v>
@@ -13904,7 +13907,7 @@
         <v>226</v>
       </c>
       <c r="E22" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="F22" t="s">
         <v>212</v>
@@ -13913,13 +13916,13 @@
         <v>322</v>
       </c>
       <c r="H22" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="I22" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="J22">
-        <v>151.5</v>
+        <v>153.5</v>
       </c>
       <c r="K22">
         <v>0</v>
@@ -14000,7 +14003,7 @@
         <v>12.6</v>
       </c>
       <c r="AK22" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AL22">
         <v>315</v>
@@ -14021,7 +14024,7 @@
         <v>1.1493</v>
       </c>
       <c r="AR22" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AS22">
         <v>1907</v>
@@ -14092,25 +14095,25 @@
         <v>226</v>
       </c>
       <c r="E23" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="F23" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="G23" t="s">
         <v>322</v>
       </c>
       <c r="H23" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="I23" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="J23">
-        <v>151.5</v>
+        <v>153.5</v>
       </c>
       <c r="K23">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="L23">
         <v>5</v>
@@ -14188,7 +14191,7 @@
         <v>11.2</v>
       </c>
       <c r="AK23" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -14209,7 +14212,7 @@
         <v>1.149</v>
       </c>
       <c r="AR23" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AS23">
         <v>1907</v>
@@ -14280,25 +14283,25 @@
         <v>226</v>
       </c>
       <c r="E24" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="F24" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="G24" t="s">
         <v>322</v>
       </c>
       <c r="H24" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="I24" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="J24">
-        <v>151.5</v>
+        <v>153.5</v>
       </c>
       <c r="K24">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="L24">
         <v>5</v>
@@ -14334,7 +14337,7 @@
         <v>0</v>
       </c>
       <c r="W24" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="X24">
         <v>85.09999999999999</v>
@@ -14376,7 +14379,7 @@
         <v>9.699999999999999</v>
       </c>
       <c r="AK24" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -14397,7 +14400,7 @@
         <v>1.1507</v>
       </c>
       <c r="AR24" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AS24">
         <v>1854</v>
@@ -14468,7 +14471,7 @@
         <v>226</v>
       </c>
       <c r="E25" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="F25" t="s">
         <v>216</v>
@@ -14477,16 +14480,16 @@
         <v>322</v>
       </c>
       <c r="H25" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="I25" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="J25">
-        <v>151.5</v>
+        <v>153.5</v>
       </c>
       <c r="K25">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="L25">
         <v>5</v>
@@ -14522,7 +14525,7 @@
         <v>0</v>
       </c>
       <c r="W25" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="X25">
         <v>82.59999999999999</v>
@@ -14564,7 +14567,7 @@
         <v>9.6</v>
       </c>
       <c r="AK25" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AL25">
         <v>45</v>
@@ -14585,7 +14588,7 @@
         <v>1.1562</v>
       </c>
       <c r="AR25" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AS25">
         <v>1687</v>
@@ -14656,22 +14659,22 @@
         <v>227</v>
       </c>
       <c r="E26" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="F26" t="s">
         <v>214</v>
       </c>
       <c r="G26" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H26" t="s">
         <v>282</v>
       </c>
       <c r="I26" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="J26">
-        <v>39.6</v>
+        <v>41.6</v>
       </c>
       <c r="K26">
         <v>0</v>
@@ -14752,7 +14755,7 @@
         <v>11.5</v>
       </c>
       <c r="AK26" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AL26">
         <v>90</v>
@@ -14773,7 +14776,7 @@
         <v>1.1628</v>
       </c>
       <c r="AR26" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AS26">
         <v>1525</v>
@@ -14844,25 +14847,25 @@
         <v>227</v>
       </c>
       <c r="E27" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="F27" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="G27" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H27" t="s">
         <v>282</v>
       </c>
       <c r="I27" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="J27">
-        <v>39.6</v>
+        <v>41.6</v>
       </c>
       <c r="K27">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="L27">
         <v>5</v>
@@ -14940,7 +14943,7 @@
         <v>10.7</v>
       </c>
       <c r="AK27" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AL27">
         <v>90</v>
@@ -14961,7 +14964,7 @@
         <v>1.1625</v>
       </c>
       <c r="AR27" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AS27">
         <v>1541</v>
@@ -15032,25 +15035,25 @@
         <v>227</v>
       </c>
       <c r="E28" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="F28" t="s">
         <v>215</v>
       </c>
       <c r="G28" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H28" t="s">
         <v>282</v>
       </c>
       <c r="I28" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="J28">
-        <v>39.6</v>
+        <v>41.6</v>
       </c>
       <c r="K28">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="L28">
         <v>5</v>
@@ -15128,7 +15131,7 @@
         <v>9.300000000000001</v>
       </c>
       <c r="AK28" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AL28">
         <v>90</v>
@@ -15149,7 +15152,7 @@
         <v>1.1635</v>
       </c>
       <c r="AR28" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AS28">
         <v>1517</v>
@@ -15220,25 +15223,25 @@
         <v>227</v>
       </c>
       <c r="E29" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="F29" t="s">
         <v>218</v>
       </c>
       <c r="G29" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H29" t="s">
         <v>282</v>
       </c>
       <c r="I29" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="J29">
-        <v>39.6</v>
+        <v>41.6</v>
       </c>
       <c r="K29">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="L29">
         <v>5</v>
@@ -15274,7 +15277,7 @@
         <v>0</v>
       </c>
       <c r="W29" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="X29">
         <v>80.2</v>
@@ -15316,7 +15319,7 @@
         <v>7.9</v>
       </c>
       <c r="AK29" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AL29">
         <v>90</v>
@@ -15337,7 +15340,7 @@
         <v>1.1676</v>
       </c>
       <c r="AR29" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AS29">
         <v>1403</v>
@@ -15408,22 +15411,22 @@
         <v>228</v>
       </c>
       <c r="E30" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="F30" t="s">
         <v>214</v>
       </c>
       <c r="G30" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H30" t="s">
         <v>283</v>
       </c>
       <c r="I30" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="J30">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="K30">
         <v>0</v>
@@ -15504,7 +15507,7 @@
         <v>8.9</v>
       </c>
       <c r="AK30" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AL30">
         <v>225</v>
@@ -15525,7 +15528,7 @@
         <v>1.1896</v>
       </c>
       <c r="AR30" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AS30">
         <v>858</v>
@@ -15596,25 +15599,25 @@
         <v>228</v>
       </c>
       <c r="E31" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="F31" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="G31" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H31" t="s">
         <v>283</v>
       </c>
       <c r="I31" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="J31">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="K31">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="L31">
         <v>5</v>
@@ -15650,7 +15653,7 @@
         <v>0</v>
       </c>
       <c r="W31" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="X31">
         <v>86.59999999999999</v>
@@ -15692,7 +15695,7 @@
         <v>12.6</v>
       </c>
       <c r="AK31" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AL31">
         <v>225</v>
@@ -15713,7 +15716,7 @@
         <v>1.1896</v>
       </c>
       <c r="AR31" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AS31">
         <v>858</v>
@@ -15784,25 +15787,25 @@
         <v>228</v>
       </c>
       <c r="E32" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="F32" t="s">
         <v>215</v>
       </c>
       <c r="G32" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H32" t="s">
         <v>283</v>
       </c>
       <c r="I32" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="J32">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="K32">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="L32">
         <v>5</v>
@@ -15838,7 +15841,7 @@
         <v>0</v>
       </c>
       <c r="W32" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="X32">
         <v>87.3</v>
@@ -15880,7 +15883,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AK32" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AL32">
         <v>225</v>
@@ -15901,7 +15904,7 @@
         <v>1.1896</v>
       </c>
       <c r="AR32" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AS32">
         <v>858</v>
@@ -15972,25 +15975,25 @@
         <v>228</v>
       </c>
       <c r="E33" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="F33" t="s">
         <v>218</v>
       </c>
       <c r="G33" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H33" t="s">
         <v>283</v>
       </c>
       <c r="I33" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="J33">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="K33">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="L33">
         <v>5</v>
@@ -16026,7 +16029,7 @@
         <v>0</v>
       </c>
       <c r="W33" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="X33">
         <v>86.90000000000001</v>
@@ -16068,7 +16071,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AK33" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AL33">
         <v>225</v>
@@ -16089,7 +16092,7 @@
         <v>1.1896</v>
       </c>
       <c r="AR33" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AS33">
         <v>858</v>
@@ -16160,22 +16163,22 @@
         <v>229</v>
       </c>
       <c r="E34" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="F34" t="s">
         <v>214</v>
       </c>
       <c r="G34" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H34" t="s">
         <v>284</v>
       </c>
       <c r="I34" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="J34">
-        <v>37.7</v>
+        <v>39.7</v>
       </c>
       <c r="K34">
         <v>0</v>
@@ -16256,7 +16259,7 @@
         <v>12.5</v>
       </c>
       <c r="AK34" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AL34">
         <v>90</v>
@@ -16277,7 +16280,7 @@
         <v>1.1896</v>
       </c>
       <c r="AR34" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AS34">
         <v>858</v>
@@ -16348,25 +16351,25 @@
         <v>229</v>
       </c>
       <c r="E35" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="F35" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="G35" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H35" t="s">
         <v>284</v>
       </c>
       <c r="I35" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="J35">
-        <v>37.7</v>
+        <v>39.7</v>
       </c>
       <c r="K35">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="L35">
         <v>5</v>
@@ -16444,7 +16447,7 @@
         <v>13.1</v>
       </c>
       <c r="AK35" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AL35">
         <v>90</v>
@@ -16465,7 +16468,7 @@
         <v>1.1896</v>
       </c>
       <c r="AR35" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AS35">
         <v>858</v>
@@ -16536,25 +16539,25 @@
         <v>229</v>
       </c>
       <c r="E36" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="F36" t="s">
         <v>215</v>
       </c>
       <c r="G36" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H36" t="s">
         <v>284</v>
       </c>
       <c r="I36" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="J36">
-        <v>37.7</v>
+        <v>39.7</v>
       </c>
       <c r="K36">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="L36">
         <v>5</v>
@@ -16632,7 +16635,7 @@
         <v>11.6</v>
       </c>
       <c r="AK36" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AL36">
         <v>90</v>
@@ -16653,7 +16656,7 @@
         <v>1.1896</v>
       </c>
       <c r="AR36" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AS36">
         <v>858</v>
@@ -16724,25 +16727,25 @@
         <v>229</v>
       </c>
       <c r="E37" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="F37" t="s">
         <v>218</v>
       </c>
       <c r="G37" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H37" t="s">
         <v>284</v>
       </c>
       <c r="I37" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="J37">
-        <v>37.7</v>
+        <v>39.7</v>
       </c>
       <c r="K37">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="L37">
         <v>5</v>
@@ -16820,7 +16823,7 @@
         <v>11.3</v>
       </c>
       <c r="AK37" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AL37">
         <v>90</v>
@@ -16841,7 +16844,7 @@
         <v>1.1578</v>
       </c>
       <c r="AR37" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AS37">
         <v>1588</v>
@@ -16850,7 +16853,7 @@
         <v>297</v>
       </c>
       <c r="AU37" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AV37">
         <v>52.1</v>
@@ -16912,25 +16915,25 @@
         <v>230</v>
       </c>
       <c r="E38" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="F38" t="s">
         <v>215</v>
       </c>
       <c r="G38" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H38" t="s">
         <v>285</v>
       </c>
       <c r="I38" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="J38">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K38">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="L38">
         <v>5</v>
@@ -17008,7 +17011,7 @@
         <v>16</v>
       </c>
       <c r="AK38" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AL38">
         <v>67.5</v>
@@ -17029,7 +17032,7 @@
         <v>1.1419</v>
       </c>
       <c r="AR38" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AS38">
         <v>2191</v>
@@ -17100,25 +17103,25 @@
         <v>230</v>
       </c>
       <c r="E39" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="F39" t="s">
         <v>218</v>
       </c>
       <c r="G39" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H39" t="s">
         <v>285</v>
       </c>
       <c r="I39" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="J39">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K39">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="L39">
         <v>5</v>
@@ -17154,7 +17157,7 @@
         <v>0</v>
       </c>
       <c r="W39" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="X39">
         <v>82.3</v>
@@ -17196,7 +17199,7 @@
         <v>14.7</v>
       </c>
       <c r="AK39" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AL39">
         <v>67.5</v>
@@ -17217,7 +17220,7 @@
         <v>1.1437</v>
       </c>
       <c r="AR39" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AS39">
         <v>2150</v>
@@ -17288,25 +17291,25 @@
         <v>230</v>
       </c>
       <c r="E40" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="F40" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="G40" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H40" t="s">
         <v>285</v>
       </c>
       <c r="I40" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="J40">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K40">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="L40">
         <v>5</v>
@@ -17342,7 +17345,7 @@
         <v>0</v>
       </c>
       <c r="W40" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="X40">
         <v>80.40000000000001</v>
@@ -17384,7 +17387,7 @@
         <v>14.9</v>
       </c>
       <c r="AK40" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AL40">
         <v>45</v>
@@ -17405,7 +17408,7 @@
         <v>1.1484</v>
       </c>
       <c r="AR40" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AS40">
         <v>1997</v>
@@ -17476,25 +17479,25 @@
         <v>230</v>
       </c>
       <c r="E41" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="F41" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="G41" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H41" t="s">
         <v>285</v>
       </c>
       <c r="I41" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="J41">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K41">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L41">
         <v>5</v>
@@ -17572,7 +17575,7 @@
         <v>17.4</v>
       </c>
       <c r="AK41" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AL41">
         <v>45</v>
@@ -17593,7 +17596,7 @@
         <v>1.1563</v>
       </c>
       <c r="AR41" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AS41">
         <v>1756</v>
@@ -17664,25 +17667,25 @@
         <v>231</v>
       </c>
       <c r="E42" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="F42" t="s">
         <v>216</v>
       </c>
       <c r="G42" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H42" t="s">
         <v>286</v>
       </c>
       <c r="I42" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="J42">
-        <v>151.6</v>
+        <v>153.6</v>
       </c>
       <c r="K42">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="L42">
         <v>5</v>
@@ -17760,7 +17763,7 @@
         <v>16.5</v>
       </c>
       <c r="AK42" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AL42">
         <v>45</v>
@@ -17781,7 +17784,7 @@
         <v>1.1653</v>
       </c>
       <c r="AR42" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AS42">
         <v>1388</v>
@@ -17852,25 +17855,25 @@
         <v>231</v>
       </c>
       <c r="E43" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="F43" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="G43" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H43" t="s">
         <v>286</v>
       </c>
       <c r="I43" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="J43">
-        <v>151.6</v>
+        <v>153.6</v>
       </c>
       <c r="K43">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="L43">
         <v>5</v>
@@ -17906,7 +17909,7 @@
         <v>0</v>
       </c>
       <c r="W43" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="X43">
         <v>77.5</v>
@@ -17948,7 +17951,7 @@
         <v>13</v>
       </c>
       <c r="AK43" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AL43">
         <v>45</v>
@@ -17969,7 +17972,7 @@
         <v>1.1711</v>
       </c>
       <c r="AR43" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AS43">
         <v>1228</v>
@@ -18040,25 +18043,25 @@
         <v>231</v>
       </c>
       <c r="E44" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="F44" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="G44" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H44" t="s">
         <v>286</v>
       </c>
       <c r="I44" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="J44">
-        <v>151.6</v>
+        <v>153.6</v>
       </c>
       <c r="K44">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L44">
         <v>5</v>
@@ -18094,7 +18097,7 @@
         <v>0</v>
       </c>
       <c r="W44" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="X44">
         <v>75.2</v>
@@ -18136,7 +18139,7 @@
         <v>14.2</v>
       </c>
       <c r="AK44" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AL44">
         <v>45</v>
@@ -18157,7 +18160,7 @@
         <v>1.1768</v>
       </c>
       <c r="AR44" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AS44">
         <v>1064</v>
@@ -18228,25 +18231,25 @@
         <v>231</v>
       </c>
       <c r="E45" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="F45" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="G45" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H45" t="s">
         <v>286</v>
       </c>
       <c r="I45" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="J45">
-        <v>151.6</v>
+        <v>153.6</v>
       </c>
       <c r="K45">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="L45">
         <v>5</v>
@@ -18282,7 +18285,7 @@
         <v>0</v>
       </c>
       <c r="W45" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="X45">
         <v>74.7</v>
@@ -18324,7 +18327,7 @@
         <v>10.6</v>
       </c>
       <c r="AK45" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AL45">
         <v>45</v>
@@ -18345,7 +18348,7 @@
         <v>1.1785</v>
       </c>
       <c r="AR45" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AS45">
         <v>1011</v>
@@ -18416,25 +18419,25 @@
         <v>232</v>
       </c>
       <c r="E46" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="F46" t="s">
         <v>217</v>
       </c>
       <c r="G46" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H46" t="s">
         <v>287</v>
       </c>
       <c r="I46" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="J46">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="K46">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="L46">
         <v>5</v>
@@ -18512,7 +18515,7 @@
         <v>16.2</v>
       </c>
       <c r="AK46" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="AL46">
         <v>180</v>
@@ -18533,7 +18536,7 @@
         <v>1.1896</v>
       </c>
       <c r="AR46" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AS46">
         <v>858</v>
@@ -18604,25 +18607,25 @@
         <v>232</v>
       </c>
       <c r="E47" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="F47" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="G47" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H47" t="s">
         <v>287</v>
       </c>
       <c r="I47" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="J47">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="K47">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="L47">
         <v>5</v>
@@ -18700,7 +18703,7 @@
         <v>17</v>
       </c>
       <c r="AK47" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="AL47">
         <v>180</v>
@@ -18721,7 +18724,7 @@
         <v>1.1896</v>
       </c>
       <c r="AR47" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AS47">
         <v>858</v>
@@ -18792,25 +18795,25 @@
         <v>232</v>
       </c>
       <c r="E48" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="F48" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="G48" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H48" t="s">
         <v>287</v>
       </c>
       <c r="I48" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="J48">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="K48">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L48">
         <v>5</v>
@@ -18846,7 +18849,7 @@
         <v>0</v>
       </c>
       <c r="W48" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="X48">
         <v>92.90000000000001</v>
@@ -18888,7 +18891,7 @@
         <v>17.4</v>
       </c>
       <c r="AK48" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="AL48">
         <v>180</v>
@@ -18909,7 +18912,7 @@
         <v>1.1896</v>
       </c>
       <c r="AR48" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AS48">
         <v>858</v>
@@ -18980,25 +18983,25 @@
         <v>232</v>
       </c>
       <c r="E49" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="F49" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="G49" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H49" t="s">
         <v>287</v>
       </c>
       <c r="I49" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="J49">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="K49">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="L49">
         <v>5</v>
@@ -19034,7 +19037,7 @@
         <v>0</v>
       </c>
       <c r="W49" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="X49">
         <v>90</v>
@@ -19076,7 +19079,7 @@
         <v>17.9</v>
       </c>
       <c r="AK49" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="AL49">
         <v>180</v>
@@ -19097,7 +19100,7 @@
         <v>1.1896</v>
       </c>
       <c r="AR49" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AS49">
         <v>858</v>
@@ -19168,25 +19171,25 @@
         <v>233</v>
       </c>
       <c r="E50" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="F50" t="s">
         <v>218</v>
       </c>
       <c r="G50" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H50" t="s">
         <v>288</v>
       </c>
       <c r="I50" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="J50">
-        <v>54</v>
+        <v>56.1</v>
       </c>
       <c r="K50">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="L50">
         <v>5</v>
@@ -19264,7 +19267,7 @@
         <v>7.4</v>
       </c>
       <c r="AK50" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AL50">
         <v>45</v>
@@ -19285,7 +19288,7 @@
         <v>1.1451</v>
       </c>
       <c r="AR50" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AS50">
         <v>1977</v>
@@ -19356,25 +19359,25 @@
         <v>233</v>
       </c>
       <c r="E51" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="F51" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="G51" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H51" t="s">
         <v>288</v>
       </c>
       <c r="I51" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="J51">
-        <v>54</v>
+        <v>56.1</v>
       </c>
       <c r="K51">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="L51">
         <v>5</v>
@@ -19410,7 +19413,7 @@
         <v>2.2</v>
       </c>
       <c r="W51" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="X51">
         <v>77</v>
@@ -19452,7 +19455,7 @@
         <v>6.8</v>
       </c>
       <c r="AK51" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AL51">
         <v>90</v>
@@ -19473,7 +19476,7 @@
         <v>1.1485</v>
       </c>
       <c r="AR51" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AS51">
         <v>1880</v>
@@ -19544,25 +19547,25 @@
         <v>233</v>
       </c>
       <c r="E52" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="F52" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="G52" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H52" t="s">
         <v>288</v>
       </c>
       <c r="I52" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="J52">
-        <v>54</v>
+        <v>56.1</v>
       </c>
       <c r="K52">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L52">
         <v>5</v>
@@ -19598,7 +19601,7 @@
         <v>2.2</v>
       </c>
       <c r="W52" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="X52">
         <v>75.59999999999999</v>
@@ -19640,7 +19643,7 @@
         <v>4.9</v>
       </c>
       <c r="AK52" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AL52">
         <v>45</v>
@@ -19661,7 +19664,7 @@
         <v>1.1517</v>
       </c>
       <c r="AR52" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AS52">
         <v>1786</v>
@@ -19732,25 +19735,25 @@
         <v>233</v>
       </c>
       <c r="E53" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="F53" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="G53" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H53" t="s">
         <v>288</v>
       </c>
       <c r="I53" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="J53">
-        <v>54</v>
+        <v>56.1</v>
       </c>
       <c r="K53">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="L53">
         <v>5</v>
@@ -19786,7 +19789,7 @@
         <v>2.2</v>
       </c>
       <c r="W53" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="X53">
         <v>74.09999999999999</v>
@@ -19828,7 +19831,7 @@
         <v>5.4</v>
       </c>
       <c r="AK53" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AL53">
         <v>45</v>
@@ -19849,7 +19852,7 @@
         <v>1.1558</v>
       </c>
       <c r="AR53" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AS53">
         <v>1668</v>
@@ -19920,22 +19923,22 @@
         <v>234</v>
       </c>
       <c r="E54" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="F54" t="s">
         <v>219</v>
       </c>
       <c r="G54" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H54" t="s">
         <v>289</v>
       </c>
       <c r="I54" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="J54">
-        <v>52.8</v>
+        <v>54.8</v>
       </c>
       <c r="K54">
         <v>2.3</v>
@@ -20016,7 +20019,7 @@
         <v>13.2</v>
       </c>
       <c r="AK54" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -20037,7 +20040,7 @@
         <v>1.1505</v>
       </c>
       <c r="AR54" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AS54">
         <v>1815</v>
@@ -20108,22 +20111,22 @@
         <v>234</v>
       </c>
       <c r="E55" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="F55" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="G55" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H55" t="s">
         <v>289</v>
       </c>
       <c r="I55" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="J55">
-        <v>52.8</v>
+        <v>54.8</v>
       </c>
       <c r="K55">
         <v>3.3</v>
@@ -20162,7 +20165,7 @@
         <v>0</v>
       </c>
       <c r="W55" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="X55">
         <v>77.8</v>
@@ -20204,7 +20207,7 @@
         <v>13.3</v>
       </c>
       <c r="AK55" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -20225,7 +20228,7 @@
         <v>1.1541</v>
       </c>
       <c r="AR55" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AS55">
         <v>1702</v>
@@ -20296,22 +20299,22 @@
         <v>234</v>
       </c>
       <c r="E56" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="F56" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="G56" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H56" t="s">
         <v>289</v>
       </c>
       <c r="I56" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="J56">
-        <v>52.8</v>
+        <v>54.8</v>
       </c>
       <c r="K56">
         <v>4.3</v>
@@ -20392,7 +20395,7 @@
         <v>13.8</v>
       </c>
       <c r="AK56" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -20413,7 +20416,7 @@
         <v>1.1572</v>
       </c>
       <c r="AR56" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AS56">
         <v>1616</v>
@@ -20484,22 +20487,22 @@
         <v>234</v>
       </c>
       <c r="E57" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="F57" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="G57" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H57" t="s">
         <v>289</v>
       </c>
       <c r="I57" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="J57">
-        <v>52.8</v>
+        <v>54.8</v>
       </c>
       <c r="K57">
         <v>5.3</v>
@@ -20538,7 +20541,7 @@
         <v>0</v>
       </c>
       <c r="W57" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="X57">
         <v>75.5</v>
@@ -20580,7 +20583,7 @@
         <v>11</v>
       </c>
       <c r="AK57" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -20601,7 +20604,7 @@
         <v>1.1606</v>
       </c>
       <c r="AR57" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AS57">
         <v>1520</v>
@@ -20672,25 +20675,25 @@
         <v>235</v>
       </c>
       <c r="E58" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="F58" t="s">
         <v>220</v>
       </c>
       <c r="G58" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H58" t="s">
         <v>290</v>
       </c>
       <c r="I58" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="J58">
-        <v>148.5</v>
+        <v>150.5</v>
       </c>
       <c r="K58">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="L58">
         <v>5</v>
@@ -20789,7 +20792,7 @@
         <v>1.1852</v>
       </c>
       <c r="AR58" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AS58">
         <v>890</v>
@@ -20860,25 +20863,25 @@
         <v>235</v>
       </c>
       <c r="E59" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="F59" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="G59" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H59" t="s">
         <v>290</v>
       </c>
       <c r="I59" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="J59">
-        <v>148.5</v>
+        <v>150.5</v>
       </c>
       <c r="K59">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L59">
         <v>5</v>
@@ -20977,7 +20980,7 @@
         <v>1.1901</v>
       </c>
       <c r="AR59" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AS59">
         <v>747</v>
@@ -21048,25 +21051,25 @@
         <v>235</v>
       </c>
       <c r="E60" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="F60" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="G60" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H60" t="s">
         <v>290</v>
       </c>
       <c r="I60" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="J60">
-        <v>148.5</v>
+        <v>150.5</v>
       </c>
       <c r="K60">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="L60">
         <v>5</v>
@@ -21165,7 +21168,7 @@
         <v>1.1944</v>
       </c>
       <c r="AR60" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AS60">
         <v>622</v>
@@ -21236,25 +21239,25 @@
         <v>235</v>
       </c>
       <c r="E61" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="F61" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="G61" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H61" t="s">
         <v>290</v>
       </c>
       <c r="I61" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="J61">
-        <v>148.5</v>
+        <v>150.5</v>
       </c>
       <c r="K61">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="L61">
         <v>5</v>
@@ -21332,7 +21335,7 @@
         <v>5.3</v>
       </c>
       <c r="AK61" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AL61">
         <v>302.6</v>
@@ -21353,7 +21356,7 @@
         <v>1.1954</v>
       </c>
       <c r="AR61" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AS61">
         <v>590</v>
@@ -21424,25 +21427,25 @@
         <v>236</v>
       </c>
       <c r="E62" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="F62" t="s">
         <v>221</v>
       </c>
       <c r="G62" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H62" t="s">
         <v>291</v>
       </c>
       <c r="I62" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="J62">
-        <v>96.8</v>
+        <v>98.8</v>
       </c>
       <c r="K62">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L62">
         <v>5</v>
@@ -21520,7 +21523,7 @@
         <v>10.1</v>
       </c>
       <c r="AK62" t="s">
-        <v>347</v>
+        <v>357</v>
       </c>
       <c r="AL62">
         <v>202.5</v>
@@ -21541,7 +21544,7 @@
         <v>1.1434</v>
       </c>
       <c r="AR62" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AS62">
         <v>2152</v>
@@ -21612,25 +21615,25 @@
         <v>236</v>
       </c>
       <c r="E63" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="F63" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="G63" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H63" t="s">
         <v>291</v>
       </c>
       <c r="I63" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="J63">
-        <v>96.8</v>
+        <v>98.8</v>
       </c>
       <c r="K63">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="L63">
         <v>5</v>
@@ -21708,7 +21711,7 @@
         <v>7.7</v>
       </c>
       <c r="AK63" t="s">
-        <v>347</v>
+        <v>357</v>
       </c>
       <c r="AL63">
         <v>202.5</v>
@@ -21729,7 +21732,7 @@
         <v>1.1471</v>
       </c>
       <c r="AR63" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AS63">
         <v>2030</v>
@@ -21800,25 +21803,25 @@
         <v>236</v>
       </c>
       <c r="E64" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="F64" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="G64" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H64" t="s">
         <v>291</v>
       </c>
       <c r="I64" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="J64">
-        <v>96.8</v>
+        <v>98.8</v>
       </c>
       <c r="K64">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="L64">
         <v>5</v>
@@ -21896,7 +21899,7 @@
         <v>6.3</v>
       </c>
       <c r="AK64" t="s">
-        <v>347</v>
+        <v>357</v>
       </c>
       <c r="AL64">
         <v>202.5</v>
@@ -21917,7 +21920,7 @@
         <v>1.153</v>
       </c>
       <c r="AR64" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AS64">
         <v>1838</v>
@@ -21988,25 +21991,25 @@
         <v>236</v>
       </c>
       <c r="E65" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="F65" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="G65" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H65" t="s">
         <v>291</v>
       </c>
       <c r="I65" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="J65">
-        <v>96.8</v>
+        <v>98.8</v>
       </c>
       <c r="K65">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="L65">
         <v>5</v>
@@ -22084,7 +22087,7 @@
         <v>5.2</v>
       </c>
       <c r="AK65" t="s">
-        <v>347</v>
+        <v>357</v>
       </c>
       <c r="AL65">
         <v>202.5</v>
@@ -22105,7 +22108,7 @@
         <v>1.1576</v>
       </c>
       <c r="AR65" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AS65">
         <v>1689</v>
@@ -22265,16 +22268,16 @@
         <v>223</v>
       </c>
       <c r="E2">
-        <v>81.3</v>
+        <v>82.3</v>
       </c>
       <c r="F2">
-        <v>79.3</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="G2" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I2" s="4">
         <v>16</v>
@@ -22283,19 +22286,19 @@
         <v>7</v>
       </c>
       <c r="K2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="L2">
-        <v>93.7</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="M2">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="N2">
-        <v>89.2</v>
+        <v>88.8</v>
       </c>
       <c r="O2">
-        <v>2853</v>
+        <v>2829</v>
       </c>
       <c r="P2" t="s">
         <v>297</v>
@@ -22327,10 +22330,10 @@
         <v>70.3</v>
       </c>
       <c r="G3" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H3" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I3" s="4">
         <v>11</v>
@@ -22383,10 +22386,10 @@
         <v>61.1</v>
       </c>
       <c r="G4" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H4" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="I4" s="4">
         <v>6</v>
@@ -22439,10 +22442,10 @@
         <v>60.4</v>
       </c>
       <c r="G5" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H5" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="I5" s="4">
         <v>6</v>
@@ -22495,10 +22498,10 @@
         <v>57.2</v>
       </c>
       <c r="G6" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H6" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="I6" s="4">
         <v>4</v>
@@ -22507,7 +22510,7 @@
         <v>1.7</v>
       </c>
       <c r="K6" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="L6">
         <v>83.5</v>
@@ -22551,10 +22554,10 @@
         <v>56.3</v>
       </c>
       <c r="G7" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H7" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="I7" s="4">
         <v>3</v>
@@ -22563,7 +22566,7 @@
         <v>1.5</v>
       </c>
       <c r="K7" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="L7">
         <v>85.40000000000001</v>
@@ -22607,10 +22610,10 @@
         <v>56.3</v>
       </c>
       <c r="G8" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H8" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="I8" s="4">
         <v>3</v>
@@ -22619,7 +22622,7 @@
         <v>1.5</v>
       </c>
       <c r="K8" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="L8">
         <v>93.8</v>
@@ -22663,10 +22666,10 @@
         <v>55</v>
       </c>
       <c r="G9" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H9" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="I9" s="4">
         <v>3</v>
@@ -22675,7 +22678,7 @@
         <v>1.2</v>
       </c>
       <c r="K9" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="L9">
         <v>84.5</v>
@@ -22719,10 +22722,10 @@
         <v>54.9</v>
       </c>
       <c r="G10" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H10" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="I10" s="4">
         <v>3</v>
@@ -22731,7 +22734,7 @@
         <v>1.2</v>
       </c>
       <c r="K10" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="L10">
         <v>86.2</v>
@@ -22775,10 +22778,10 @@
         <v>54.9</v>
       </c>
       <c r="G11" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H11" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="I11" s="4">
         <v>3</v>
@@ -22831,10 +22834,10 @@
         <v>54.5</v>
       </c>
       <c r="G12" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H12" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="I12" s="4">
         <v>2</v>
@@ -22843,7 +22846,7 @@
         <v>1.1</v>
       </c>
       <c r="K12" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="L12">
         <v>91.90000000000001</v>
@@ -22887,10 +22890,10 @@
         <v>54.4</v>
       </c>
       <c r="G13" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H13" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="I13" s="4">
         <v>2</v>
@@ -22899,7 +22902,7 @@
         <v>1.1</v>
       </c>
       <c r="K13" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="L13">
         <v>84.09999999999999</v>
@@ -22943,10 +22946,10 @@
         <v>47.2</v>
       </c>
       <c r="G14" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H14" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="I14" s="4">
         <v>-2</v>
@@ -22955,7 +22958,7 @@
         <v>-0.7</v>
       </c>
       <c r="K14" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="L14">
         <v>85</v>
@@ -22999,10 +23002,10 @@
         <v>46.2</v>
       </c>
       <c r="G15" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H15" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="I15" s="4">
         <v>-2</v>
@@ -23011,7 +23014,7 @@
         <v>-0.9</v>
       </c>
       <c r="K15" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="L15">
         <v>76.3</v>
@@ -23055,10 +23058,10 @@
         <v>41.8</v>
       </c>
       <c r="G16" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H16" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="I16" s="4">
         <v>-5</v>
@@ -23067,7 +23070,7 @@
         <v>-2</v>
       </c>
       <c r="K16" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="L16">
         <v>93.8</v>
@@ -23111,10 +23114,10 @@
         <v>31.5</v>
       </c>
       <c r="G17" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H17" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="I17" s="4">
         <v>-10</v>
@@ -23123,7 +23126,7 @@
         <v>-4.4</v>
       </c>
       <c r="K17" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="L17">
         <v>85.7</v>
